--- a/output/pdf_financials_xlsx/WT.H.xlsx
+++ b/output/pdf_financials_xlsx/WT.H.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.114764</v>
+        <v>-0.114764</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.312908</v>
+        <v>-0.312908</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.396629</v>
+        <v>-0.396629</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-0.160393</v>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.114764</v>
+        <v>-0.114764</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.312908</v>
+        <v>-0.312908</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.396629</v>
+        <v>-0.396629</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.160393</v>
@@ -1534,13 +1534,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.114764</v>
+        <v>-0.114764</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.312908</v>
+        <v>-0.312908</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.396629</v>
+        <v>-0.396629</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.160393</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.498974</v>
+        <v>-0.498974</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.955675</v>
+        <v>-1.955675</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1.983145</v>
+        <v>-1.983145</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1.782144</v>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.114764</v>
+        <v>-0.114764</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.312908</v>
+        <v>-0.312908</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.396629</v>
+        <v>-0.396629</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.160393</v>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.114764</v>
+        <v>-0.114764</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.312908</v>
+        <v>-0.312908</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.396629</v>
+        <v>-0.396629</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.160393</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -5112,43 +5112,43 @@
         <v>0.127253</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.127253</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.127253</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.127253</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.151161</v>
       </c>
     </row>
     <row r="93">
@@ -5432,13 +5432,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.114764</v>
+        <v>-0.114764</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.312908</v>
+        <v>-0.312908</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.396629</v>
+        <v>-0.396629</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.160393</v>
@@ -8018,7 +8018,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -9108,7 +9112,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10918,7 +10926,11 @@
           <t>Share-based payments reserve 151,161</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -11860,7 +11872,11 @@
           <t>SHARE-BASED PAYMENTS RESERVE</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -12204,7 +12220,11 @@
           <t>SHARE-BASED PAYMENTS RESERVE</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.127253</v>
       </c>
@@ -20698,16 +20718,16 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0.114764</v>
+        <v>-0.114764</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>0.312908</v>
+        <v>-0.312908</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.396629</v>
+        <v>-0.396629</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>0.160393</v>
+        <v>-0.160393</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WT.H.xlsx
+++ b/output/pdf_financials_xlsx/WT.H.xlsx
@@ -954,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.037196</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.044161</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -969,16 +969,16 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.002292</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.005773</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.005756</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00159</v>
       </c>
     </row>
     <row r="13">
@@ -1759,10 +1759,10 @@
         <v>-0.198135</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.30192</v>
+        <v>-0.339116</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.761929</v>
+        <v>-0.80609</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0.090181</v>
@@ -1774,16 +1774,16 @@
         <v>-0.072091</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.168761</v>
+        <v>-0.171053</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.050389</v>
+        <v>-0.056162</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.066467</v>
+        <v>-0.072223</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.034604</v>
+        <v>-0.036194</v>
       </c>
     </row>
     <row r="28">
@@ -1857,10 +1857,10 @@
         <v>-0.198135</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.30192</v>
+        <v>-0.339116</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.761929</v>
+        <v>-0.80609</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.090181</v>
@@ -1872,16 +1872,16 @@
         <v>-0.072091</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.168761</v>
+        <v>-0.171053</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.050389</v>
+        <v>-0.056162</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.066467</v>
+        <v>-0.072223</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.034604</v>
+        <v>-0.036194</v>
       </c>
     </row>
     <row r="30">
@@ -2101,31 +2101,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.665525</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.359187</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.017169</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.004761</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.484138</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.01055</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.013093</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.112261</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.120528</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.429394</v>
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.665525</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.359187</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.017169</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.004761</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.484138</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.01055</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.013093</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.112261</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.120528</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.429394</v>
@@ -2787,31 +2787,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.669442</v>
+        <v>0.003917</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.391878</v>
+        <v>0.032691</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.018301</v>
+        <v>0.001132</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.006687</v>
+        <v>0.001926</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.497478</v>
+        <v>0.01334</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.037251</v>
+        <v>0.026701</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.028554</v>
+        <v>0.015461</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.191483</v>
+        <v>0.079222</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.123282</v>
+        <v>0.002754</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.0083</v>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -20626,7 +20626,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
